--- a/개발문서/결재목록.xlsx
+++ b/개발문서/결재목록.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\SOURCE\WOO\COUPANG\네이버자동주문\개발문서\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E16B2A3D-D031-44CA-8E0F-297974A884C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DF6541D2-5A5A-42B2-9323-AE927E56A19E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="18240" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="687" uniqueCount="147">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="688" uniqueCount="148">
   <si>
     <t>수취인</t>
   </si>
@@ -464,6 +464,10 @@
   </si>
   <si>
     <t>2차비밀번호</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>카드번호</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1081,7 +1085,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L178"/>
+  <dimension ref="A1:M178"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="19.25" bestFit="1" customWidth="1"/>
@@ -1091,12 +1095,13 @@
     <col min="6" max="6" width="41.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12" customWidth="1"/>
     <col min="8" max="8" width="78.375" customWidth="1"/>
+    <col min="9" max="9" width="11.375" customWidth="1"/>
     <col min="10" max="10" width="12.625" customWidth="1"/>
     <col min="11" max="11" width="19.75" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="12.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1133,8 +1138,11 @@
       <c r="L1" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M1" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="11" t="s">
         <v>11</v>
       </c>
@@ -1165,8 +1173,11 @@
       <c r="K2" s="7" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M2">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="10" t="s">
         <v>20</v>
       </c>
@@ -1197,8 +1208,11 @@
       <c r="K3" s="7" t="s">
         <v>21</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="M3">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A4" s="10" t="s">
         <v>22</v>
       </c>
@@ -1230,7 +1244,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="11" t="s">
         <v>27</v>
       </c>
@@ -1262,7 +1276,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" s="10" t="s">
         <v>29</v>
       </c>
@@ -1294,7 +1308,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" s="11" t="s">
         <v>31</v>
       </c>
@@ -1327,7 +1341,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A8" s="10" t="s">
         <v>36</v>
       </c>
@@ -1359,7 +1373,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A9" s="11" t="s">
         <v>38</v>
       </c>
@@ -1391,7 +1405,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A10" s="10" t="s">
         <v>40</v>
       </c>
@@ -1423,7 +1437,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A11" s="11" t="s">
         <v>45</v>
       </c>
@@ -1455,7 +1469,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A12" s="10" t="s">
         <v>47</v>
       </c>
@@ -1487,7 +1501,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A13" s="11" t="s">
         <v>49</v>
       </c>
@@ -1519,7 +1533,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A14" s="10" t="s">
         <v>54</v>
       </c>
@@ -1551,7 +1565,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A15" s="11" t="s">
         <v>56</v>
       </c>
@@ -1583,7 +1597,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A16" s="10" t="s">
         <v>58</v>
       </c>
@@ -4316,7 +4330,7 @@
   <conditionalFormatting sqref="A28:A178">
     <cfRule type="duplicateValues" dxfId="16" priority="102"/>
   </conditionalFormatting>
-  <conditionalFormatting sqref="K1:K1048576 L1">
+  <conditionalFormatting sqref="K1:K1048576 L1:M1">
     <cfRule type="duplicateValues" dxfId="15" priority="9"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="K2:K3">
